--- a/product_surveys/011_new_beverage_flavor_feedback_survey--product_surveys.xlsx
+++ b/product_surveys/011_new_beverage_flavor_feedback_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'local_store',_'value':_'local_store'}</t>
+          <t>local_store</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Local store', 'value': 'Local store'}</t>
+          <t>Local store</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Online', 'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'jotform',_'value':_'jotform'}</t>
+          <t>jotform</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'JotForm', 'value': 'JotForm'}</t>
+          <t>JotForm</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
